--- a/api/AMV_report.xlsx
+++ b/api/AMV_report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Automation\Project Automation CTD\mvr-live\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA987C5-D924-4CA7-99B8-C61226C801E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C0B01B-DBDE-4C36-8DDF-B3F63AD9D50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
   <si>
     <t>Product Information</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Product Name</t>
   </si>
   <si>
-    <t>Avanafil</t>
-  </si>
-  <si>
     <t>Active Ingredient</t>
   </si>
   <si>
@@ -66,12 +63,6 @@
     <t>HPLC ID</t>
   </si>
   <si>
-    <t>QC-196</t>
-  </si>
-  <si>
-    <t>CPL/WS/25/AVN/038</t>
-  </si>
-  <si>
     <t>15048002-AVN</t>
   </si>
   <si>
@@ -312,7 +303,13 @@
     <t>Starting Material/Product</t>
   </si>
   <si>
-    <t>SM</t>
+    <t>QC-195</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
+    <t>balafil</t>
   </si>
 </sst>
 </file>
@@ -405,7 +402,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -441,11 +438,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -501,11 +535,26 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,6 +762,12 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.11419518604692815"/>
+                  <c:y val="0.14096729065043476"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
             </c:trendlineLbl>
           </c:trendline>
@@ -723,19 +778,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.1215</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13500000000000001</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.15</c:v>
+                  <c:v>0.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.16500000000000001</c:v>
+                  <c:v>0.72</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.18149999999999999</c:v>
+                  <c:v>0.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -744,22 +799,22 @@
             <c:numRef>
               <c:f>'Validation Data'!$J$95:$J$99</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8032482.5</c:v>
+                  <c:v>8021450</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9103237</c:v>
+                  <c:v>8421780</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10122452.5</c:v>
+                  <c:v>8846230</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11136603.5</c:v>
+                  <c:v>9218540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12235850</c:v>
+                  <c:v>9587910</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -786,19 +841,10 @@
         <c:axId val="59757934"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.12000000000000001"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -868,19 +914,10 @@
         <c:axId val="22783818"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="8000000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1196,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1204,120 +1241,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2">
+        <v>99.66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
-        <v>99.66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="B15" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
     </row>
+    <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A11:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1335,56 +1381,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="A1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="A3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4">
         <v>10120780</v>
@@ -1408,7 +1454,7 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6">
         <f>AVERAGE(B5:G5)</f>
@@ -1423,7 +1469,7 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="7">
         <f>STDEV(B5:G5)</f>
@@ -1438,7 +1484,7 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="8">
         <f>B7/B6*100</f>
@@ -1453,10 +1499,10 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" s="7">
-        <f>'Product Info'!B12</f>
+        <f>'Product Info'!B14</f>
         <v>99.66</v>
       </c>
       <c r="C9" s="4"/>
@@ -1468,31 +1514,31 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4">
         <v>10084389</v>
@@ -1516,7 +1562,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13" s="6">
         <f>AVERAGE(B12:G12)</f>
@@ -1531,7 +1577,7 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <f>STDEV(B12:G12)</f>
@@ -1546,7 +1592,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <f>B14/B13*100</f>
@@ -1561,10 +1607,10 @@
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" s="7">
-        <f>'Product Info'!B12</f>
+        <f>'Product Info'!B14</f>
         <v>99.66</v>
       </c>
       <c r="C16" s="4"/>
@@ -1575,44 +1621,44 @@
       <c r="H16" s="4"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="A19" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B21" s="9">
         <v>8033543</v>
@@ -1639,7 +1685,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6">
         <v>8031422</v>
@@ -1666,7 +1712,7 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="7" t="str">
@@ -1687,7 +1733,7 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B24" s="11">
         <f>IFERROR(AVERAGEIF(B21:B23,"&lt;&gt;"),"")</f>
@@ -1717,7 +1763,7 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B25" s="7">
         <f>IF(COUNTA(B21:B23)=0,"",STDEV(B21:B23)/B24*100)</f>
@@ -1738,19 +1784,19 @@
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -1758,7 +1804,7 @@
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B28" s="9">
         <v>11139702</v>
@@ -1780,7 +1826,7 @@
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B29" s="6">
         <v>11133505</v>
@@ -1802,7 +1848,7 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="7" t="str">
@@ -1820,7 +1866,7 @@
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B31" s="11">
         <f>IFERROR(AVERAGEIF(B28:B30,"&lt;&gt;"),"")</f>
@@ -1844,7 +1890,7 @@
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B32" s="7">
         <f>IF(COUNTA(B28:B30)=0,"",STDEV(B28:B30)/B31*100)</f>
@@ -1861,44 +1907,44 @@
       <c r="H32" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
     </row>
     <row r="35" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B36" s="9">
         <v>8181863</v>
@@ -1925,7 +1971,7 @@
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B37" s="6">
         <v>8223041</v>
@@ -1952,7 +1998,7 @@
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B38" s="9">
         <v>8194699</v>
@@ -1979,7 +2025,7 @@
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B39" s="13">
         <f>IFERROR(AVERAGEIF(B36:B38,"&lt;&gt;"),"")</f>
@@ -2009,7 +2055,7 @@
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B40" s="7">
         <f>IF(COUNTA(B36:B38)=0,"",STDEV(B36:B38)/B39*100)</f>
@@ -2029,29 +2075,29 @@
       <c r="H40" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
+      <c r="A42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -2060,10 +2106,10 @@
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C44" s="6">
         <v>10054095</v>
@@ -2080,7 +2126,7 @@
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C45" s="9">
         <v>10171758</v>
@@ -2097,7 +2143,7 @@
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C46" s="6">
         <v>10254155</v>
@@ -2114,7 +2160,7 @@
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47" s="13">
         <f>AVERAGE(C44:C46)</f>
@@ -2132,7 +2178,7 @@
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C48" s="7">
         <f>STDEV(C44:C46)</f>
@@ -2150,7 +2196,7 @@
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C49" s="8">
         <f>IFERROR(C48/C47*100,"")</f>
@@ -2167,10 +2213,10 @@
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C51" s="6">
         <v>10273395</v>
@@ -2187,7 +2233,7 @@
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C52" s="9">
         <v>10259195</v>
@@ -2204,7 +2250,7 @@
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C53" s="6">
         <v>10268662</v>
@@ -2221,7 +2267,7 @@
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C54" s="13">
         <f>AVERAGE(C51:C53)</f>
@@ -2239,7 +2285,7 @@
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C55" s="7">
         <f>STDEV(C51:C53)</f>
@@ -2257,7 +2303,7 @@
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C56" s="8">
         <f>IFERROR(C55/C54*100,"")</f>
@@ -2274,10 +2320,10 @@
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C58" s="6">
         <v>10238001</v>
@@ -2294,7 +2340,7 @@
     <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C59" s="9">
         <v>10330471</v>
@@ -2311,7 +2357,7 @@
     <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C60" s="6">
         <v>10317825</v>
@@ -2328,7 +2374,7 @@
     <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C61" s="13">
         <f>AVERAGE(C58:C60)</f>
@@ -2346,7 +2392,7 @@
     <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C62" s="7">
         <f>STDEV(C58:C60)</f>
@@ -2364,7 +2410,7 @@
     <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C63" s="8">
         <f>IFERROR(C62/C61*100,"")</f>
@@ -2380,49 +2426,49 @@
       <c r="H63" s="5"/>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
+      <c r="A65" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C67" s="6">
         <v>10193883</v>
@@ -2451,7 +2497,7 @@
     <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C68" s="9">
         <v>10189922</v>
@@ -2468,7 +2514,7 @@
     <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="8" t="str">
@@ -2482,10 +2528,10 @@
     </row>
     <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C70" s="6">
         <v>9966185</v>
@@ -2514,7 +2560,7 @@
     <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C71" s="9">
         <v>10013382</v>
@@ -2531,7 +2577,7 @@
     <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="8" t="str">
@@ -2545,10 +2591,10 @@
     </row>
     <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C73" s="6">
         <v>9952769</v>
@@ -2577,7 +2623,7 @@
     <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C74" s="9">
         <v>9959356</v>
@@ -2594,7 +2640,7 @@
     <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="8" t="str">
@@ -2608,10 +2654,10 @@
     </row>
     <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C76" s="6">
         <v>10068648</v>
@@ -2640,7 +2686,7 @@
     <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C77" s="9">
         <v>10023760</v>
@@ -2657,7 +2703,7 @@
     <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
       <c r="B78" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="8" t="str">
@@ -2670,29 +2716,29 @@
       <c r="H78" s="5"/>
     </row>
     <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
+      <c r="A80" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" s="21"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
     </row>
     <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -2701,10 +2747,10 @@
     </row>
     <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C82" s="9">
         <v>10250991</v>
@@ -2721,7 +2767,7 @@
     <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C83" s="6">
         <v>10424630</v>
@@ -2734,10 +2780,10 @@
     </row>
     <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C84" s="6">
         <v>10265336</v>
@@ -2754,7 +2800,7 @@
     <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C85" s="9">
         <v>10452302</v>
@@ -2766,46 +2812,46 @@
       <c r="H85" s="4"/>
     </row>
     <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
+      <c r="A87" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="21"/>
     </row>
     <row r="88" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="F88" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="G88" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="H88" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B89" s="15">
         <v>2.9759999999999999E-3</v>
@@ -2829,7 +2875,7 @@
     </row>
     <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B90" s="17">
         <v>9.0189999999999992E-3</v>
@@ -2846,63 +2892,63 @@
       <c r="H90" s="5"/>
     </row>
     <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="19"/>
+      <c r="A93" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B93" s="21"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="21"/>
+      <c r="G93" s="21"/>
+      <c r="H93" s="21"/>
     </row>
     <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I94" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J94" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I95">
-        <v>0.1215</v>
-      </c>
-      <c r="J95">
-        <v>8032482.5</v>
+      <c r="I95" s="19">
+        <v>0.12</v>
+      </c>
+      <c r="J95" s="20">
+        <v>8021450</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I96">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="J96">
-        <v>9103237</v>
+      <c r="I96" s="19">
+        <v>0.32</v>
+      </c>
+      <c r="J96" s="20">
+        <v>8421780</v>
       </c>
     </row>
     <row r="97" spans="9:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I97">
-        <v>0.15</v>
-      </c>
-      <c r="J97">
-        <v>10122452.5</v>
+      <c r="I97" s="19">
+        <v>0.52</v>
+      </c>
+      <c r="J97" s="20">
+        <v>8846230</v>
       </c>
     </row>
     <row r="98" spans="9:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I98">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="J98">
-        <v>11136603.5</v>
+      <c r="I98" s="19">
+        <v>0.72</v>
+      </c>
+      <c r="J98" s="20">
+        <v>9218540</v>
       </c>
     </row>
     <row r="99" spans="9:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I99">
-        <v>0.18149999999999999</v>
-      </c>
-      <c r="J99">
-        <v>12235850</v>
+      <c r="I99" s="19">
+        <v>0.92</v>
+      </c>
+      <c r="J99" s="20">
+        <v>9587910</v>
       </c>
     </row>
   </sheetData>

--- a/api/AMV_report.xlsx
+++ b/api/AMV_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Automation\Project Automation CTD\mvr-live\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C0B01B-DBDE-4C36-8DDF-B3F63AD9D50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A3D3FD-AFF7-4FC5-8BB6-1CB38B3FE2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,9 +282,6 @@
     <t>Conc (mg/ml)</t>
   </si>
   <si>
-    <t>Avanafil 200mg Tablets</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -306,10 +303,13 @@
     <t>QC-195</t>
   </si>
   <si>
-    <t>sm</t>
-  </si>
-  <si>
-    <t>balafil</t>
+    <t>p</t>
+  </si>
+  <si>
+    <t>sildenafil</t>
+  </si>
+  <si>
+    <t>Tadalafil 200mg Tablets</t>
   </si>
 </sst>
 </file>
@@ -544,9 +544,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -555,6 +552,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1251,15 +1251,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1267,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1280,16 +1280,16 @@
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1305,32 +1305,36 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2">
         <v>1546</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
-        <v>86</v>
+      <c r="A11" s="22" t="s">
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="2"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1381,16 +1385,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
